--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782690</v>
       </c>
       <c r="B2" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125783068</v>
       </c>
       <c r="B3" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125783690</v>
       </c>
       <c r="B4" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125783208</v>
       </c>
       <c r="B5" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125782282</v>
       </c>
       <c r="B6" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>125783196</v>
       </c>
       <c r="B9" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782690</v>
       </c>
       <c r="B2" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125783068</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125783690</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125783208</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125782282</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>125783196</v>
       </c>
       <c r="B9" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782690</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125783068</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125783690</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125783208</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125782282</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125784308</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>125783709</v>
       </c>
       <c r="B8" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>125783196</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782690</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125783068</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125783690</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125783208</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125782282</v>
       </c>
       <c r="B6" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125784308</v>
       </c>
       <c r="B7" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>125783709</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>125783196</v>
       </c>
       <c r="B9" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1508,7 +1508,7 @@
         <v>129476135</v>
       </c>
       <c r="B10" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129476158</v>
       </c>
       <c r="B11" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476132</v>
+        <v>129476168</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,42 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381411</v>
+        <v>381310</v>
       </c>
       <c r="R12" t="n">
-        <v>6838786</v>
+        <v>6838877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1789,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1807,7 +1799,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476168</v>
+        <v>129476132</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,34 +1837,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381310</v>
+        <v>381411</v>
       </c>
       <c r="R13" t="n">
-        <v>6838877</v>
+        <v>6838786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1944,7 @@
         <v>129476123</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129476120</v>
       </c>
       <c r="B15" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129476145</v>
       </c>
       <c r="B16" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476161</v>
+        <v>129476119</v>
       </c>
       <c r="B17" t="n">
-        <v>79149</v>
+        <v>79694</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381371</v>
+        <v>381396</v>
       </c>
       <c r="R17" t="n">
-        <v>6838792</v>
+        <v>6838745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,24 +2351,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2385,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476162</v>
+        <v>129476161</v>
       </c>
       <c r="B18" t="n">
-        <v>79149</v>
+        <v>79154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381304</v>
+        <v>381371</v>
       </c>
       <c r="R18" t="n">
-        <v>6838862</v>
+        <v>6838792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2465,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,8 +2458,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476148</v>
+        <v>129476162</v>
       </c>
       <c r="B19" t="n">
-        <v>81055</v>
+        <v>79154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381218</v>
+        <v>381304</v>
       </c>
       <c r="R19" t="n">
-        <v>6838830</v>
+        <v>6838862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476119</v>
+        <v>129476148</v>
       </c>
       <c r="B20" t="n">
-        <v>79689</v>
+        <v>81060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381396</v>
+        <v>381218</v>
       </c>
       <c r="R20" t="n">
-        <v>6838745</v>
+        <v>6838830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,7 +2709,7 @@
         <v>129476169</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>129476154</v>
       </c>
       <c r="B22" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129476141</v>
       </c>
       <c r="B23" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476150</v>
+        <v>129476131</v>
       </c>
       <c r="B24" t="n">
-        <v>78827</v>
+        <v>90619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381228</v>
+        <v>381232</v>
       </c>
       <c r="R24" t="n">
-        <v>6838960</v>
+        <v>6838826</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476156</v>
+        <v>129476150</v>
       </c>
       <c r="B25" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381423</v>
+        <v>381228</v>
       </c>
       <c r="R25" t="n">
-        <v>6838921</v>
+        <v>6838960</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476131</v>
+        <v>129476156</v>
       </c>
       <c r="B26" t="n">
-        <v>90613</v>
+        <v>78832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381232</v>
+        <v>381423</v>
       </c>
       <c r="R26" t="n">
-        <v>6838826</v>
+        <v>6838921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476137</v>
+        <v>129476124</v>
       </c>
       <c r="B27" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>381233</v>
+        <v>381252</v>
       </c>
       <c r="R27" t="n">
-        <v>6838957</v>
+        <v>6838815</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476124</v>
+        <v>129476137</v>
       </c>
       <c r="B28" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>381252</v>
+        <v>381233</v>
       </c>
       <c r="R28" t="n">
-        <v>6838815</v>
+        <v>6838957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,7 +3565,7 @@
         <v>129476172</v>
       </c>
       <c r="B29" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129476153</v>
       </c>
       <c r="B30" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>129476170</v>
       </c>
       <c r="B31" t="n">
-        <v>78078</v>
+        <v>78083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>129476160</v>
       </c>
       <c r="B32" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476130</v>
+        <v>129476125</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381290</v>
+        <v>381441</v>
       </c>
       <c r="R33" t="n">
-        <v>6839072</v>
+        <v>6838763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476125</v>
+        <v>129476130</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381441</v>
+        <v>381290</v>
       </c>
       <c r="R34" t="n">
-        <v>6838763</v>
+        <v>6839072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,32 +4204,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476147</v>
+        <v>129476167</v>
       </c>
       <c r="B35" t="n">
-        <v>57834</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>381339</v>
+        <v>381331</v>
       </c>
       <c r="R35" t="n">
-        <v>6838869</v>
+        <v>6838974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,32 +4311,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476167</v>
+        <v>129476147</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>57839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>381331</v>
+        <v>381339</v>
       </c>
       <c r="R36" t="n">
-        <v>6838974</v>
+        <v>6838869</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4421,7 +4421,7 @@
         <v>129476121</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>129476133</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>129476128</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>129476146</v>
       </c>
       <c r="B40" t="n">
-        <v>91869</v>
+        <v>91875</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476142</v>
+        <v>129476127</v>
       </c>
       <c r="B41" t="n">
-        <v>78828</v>
+        <v>79665</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381360</v>
+        <v>381181</v>
       </c>
       <c r="R41" t="n">
-        <v>6838853</v>
+        <v>6839245</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476127</v>
+        <v>129476157</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>78832</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4973,21 +4973,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381181</v>
+        <v>381464</v>
       </c>
       <c r="R42" t="n">
-        <v>6839245</v>
+        <v>6838872</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476144</v>
+        <v>129476151</v>
       </c>
       <c r="B43" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381292</v>
+        <v>381200</v>
       </c>
       <c r="R43" t="n">
-        <v>6838844</v>
+        <v>6839267</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5179,7 +5179,7 @@
         <v>129476140</v>
       </c>
       <c r="B44" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476157</v>
+        <v>129476144</v>
       </c>
       <c r="B45" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381464</v>
+        <v>381292</v>
       </c>
       <c r="R45" t="n">
-        <v>6838872</v>
+        <v>6838844</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476151</v>
+        <v>129476142</v>
       </c>
       <c r="B46" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381200</v>
+        <v>381360</v>
       </c>
       <c r="R46" t="n">
-        <v>6839267</v>
+        <v>6838853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476174</v>
+        <v>129476143</v>
       </c>
       <c r="B47" t="n">
-        <v>78473</v>
+        <v>78833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381317</v>
+        <v>381307</v>
       </c>
       <c r="R47" t="n">
-        <v>6839120</v>
+        <v>6838866</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476149</v>
+        <v>129476174</v>
       </c>
       <c r="B48" t="n">
-        <v>78827</v>
+        <v>78478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381441</v>
+        <v>381317</v>
       </c>
       <c r="R48" t="n">
-        <v>6838759</v>
+        <v>6839120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476143</v>
+        <v>129476149</v>
       </c>
       <c r="B49" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381307</v>
+        <v>381441</v>
       </c>
       <c r="R49" t="n">
-        <v>6838866</v>
+        <v>6838759</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476138</v>
+        <v>129476164</v>
       </c>
       <c r="B50" t="n">
-        <v>78828</v>
+        <v>79154</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381200</v>
+        <v>381410</v>
       </c>
       <c r="R50" t="n">
-        <v>6839267</v>
+        <v>6838936</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5928,7 +5928,7 @@
         <v>129476171</v>
       </c>
       <c r="B51" t="n">
-        <v>78078</v>
+        <v>78083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>129476122</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476164</v>
+        <v>129476138</v>
       </c>
       <c r="B53" t="n">
-        <v>79149</v>
+        <v>78833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381410</v>
+        <v>381200</v>
       </c>
       <c r="R53" t="n">
-        <v>6838936</v>
+        <v>6839267</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476163</v>
+        <v>129476166</v>
       </c>
       <c r="B54" t="n">
-        <v>79149</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381325</v>
+        <v>381368</v>
       </c>
       <c r="R54" t="n">
-        <v>6838970</v>
+        <v>6838740</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6356,7 +6356,7 @@
         <v>129476118</v>
       </c>
       <c r="B55" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476166</v>
+        <v>129476163</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79154</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381368</v>
+        <v>381325</v>
       </c>
       <c r="R56" t="n">
-        <v>6838740</v>
+        <v>6838970</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476155</v>
+        <v>129476136</v>
       </c>
       <c r="B57" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381382</v>
+        <v>381421</v>
       </c>
       <c r="R57" t="n">
-        <v>6838965</v>
+        <v>6838767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,10 +6674,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476159</v>
+        <v>129476155</v>
       </c>
       <c r="B58" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R58" t="n">
-        <v>6838853</v>
+        <v>6838965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476136</v>
+        <v>129476159</v>
       </c>
       <c r="B59" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381421</v>
+        <v>381360</v>
       </c>
       <c r="R59" t="n">
-        <v>6838767</v>
+        <v>6838853</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6891,7 +6891,7 @@
         <v>129476129</v>
       </c>
       <c r="B60" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>129476126</v>
       </c>
       <c r="B61" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>129476139</v>
       </c>
       <c r="B62" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>129476173</v>
       </c>
       <c r="B63" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1508,7 +1508,7 @@
         <v>129476135</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129476158</v>
       </c>
       <c r="B11" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476168</v>
+        <v>129476132</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381310</v>
+        <v>381411</v>
       </c>
       <c r="R12" t="n">
-        <v>6838877</v>
+        <v>6838786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1797,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1799,7 +1807,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476132</v>
+        <v>129476168</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,42 +1845,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381411</v>
+        <v>381310</v>
       </c>
       <c r="R13" t="n">
-        <v>6838786</v>
+        <v>6838877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1944,7 @@
         <v>129476123</v>
       </c>
       <c r="B14" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129476120</v>
       </c>
       <c r="B15" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129476145</v>
       </c>
       <c r="B16" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476119</v>
+        <v>129476161</v>
       </c>
       <c r="B17" t="n">
-        <v>79694</v>
+        <v>79155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381396</v>
+        <v>381371</v>
       </c>
       <c r="R17" t="n">
-        <v>6838745</v>
+        <v>6838792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,8 +2351,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2369,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476161</v>
+        <v>129476162</v>
       </c>
       <c r="B18" t="n">
-        <v>79154</v>
+        <v>79155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381371</v>
+        <v>381304</v>
       </c>
       <c r="R18" t="n">
-        <v>6838792</v>
+        <v>6838862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2455,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2465,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,24 +2474,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476162</v>
+        <v>129476148</v>
       </c>
       <c r="B19" t="n">
-        <v>79154</v>
+        <v>81061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381304</v>
+        <v>381218</v>
       </c>
       <c r="R19" t="n">
-        <v>6838862</v>
+        <v>6838830</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476148</v>
+        <v>129476169</v>
       </c>
       <c r="B20" t="n">
-        <v>81060</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381218</v>
+        <v>381326</v>
       </c>
       <c r="R20" t="n">
-        <v>6838830</v>
+        <v>6838973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,32 +2706,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476169</v>
+        <v>129476119</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>79695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381326</v>
+        <v>381396</v>
       </c>
       <c r="R21" t="n">
-        <v>6838973</v>
+        <v>6838745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B22" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R22" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,7 +2920,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B23" t="n">
         <v>78833</v>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R23" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476131</v>
+        <v>129476150</v>
       </c>
       <c r="B24" t="n">
-        <v>90619</v>
+        <v>78833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381232</v>
+        <v>381228</v>
       </c>
       <c r="R24" t="n">
-        <v>6838826</v>
+        <v>6838960</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476150</v>
+        <v>129476156</v>
       </c>
       <c r="B25" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381228</v>
+        <v>381423</v>
       </c>
       <c r="R25" t="n">
-        <v>6838960</v>
+        <v>6838921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476156</v>
+        <v>129476131</v>
       </c>
       <c r="B26" t="n">
-        <v>78832</v>
+        <v>90620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381423</v>
+        <v>381232</v>
       </c>
       <c r="R26" t="n">
-        <v>6838921</v>
+        <v>6838826</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,7 +3351,7 @@
         <v>129476124</v>
       </c>
       <c r="B27" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>129476137</v>
       </c>
       <c r="B28" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129476172</v>
       </c>
       <c r="B29" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129476153</v>
       </c>
       <c r="B30" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>129476170</v>
       </c>
       <c r="B31" t="n">
-        <v>78083</v>
+        <v>78084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476160</v>
+        <v>129476125</v>
       </c>
       <c r="B32" t="n">
-        <v>78832</v>
+        <v>79666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381216</v>
+        <v>381441</v>
       </c>
       <c r="R32" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476125</v>
+        <v>129476130</v>
       </c>
       <c r="B33" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381441</v>
+        <v>381290</v>
       </c>
       <c r="R33" t="n">
-        <v>6838763</v>
+        <v>6839072</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476130</v>
+        <v>129476160</v>
       </c>
       <c r="B34" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381290</v>
+        <v>381216</v>
       </c>
       <c r="R34" t="n">
-        <v>6839072</v>
+        <v>6838831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4207,7 +4207,7 @@
         <v>129476167</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>129476147</v>
       </c>
       <c r="B36" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476121</v>
+        <v>129476133</v>
       </c>
       <c r="B37" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,34 +4429,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381322</v>
+        <v>381329</v>
       </c>
       <c r="R37" t="n">
-        <v>6839022</v>
+        <v>6838937</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4496,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4506,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4533,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476133</v>
+        <v>129476128</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>79666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,42 +4544,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>381329</v>
+        <v>381183</v>
       </c>
       <c r="R38" t="n">
-        <v>6838937</v>
+        <v>6839285</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476128</v>
+        <v>129476121</v>
       </c>
       <c r="B39" t="n">
-        <v>79665</v>
+        <v>79695</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381183</v>
+        <v>381322</v>
       </c>
       <c r="R39" t="n">
-        <v>6839285</v>
+        <v>6839022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4750,7 +4750,7 @@
         <v>129476146</v>
       </c>
       <c r="B40" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476127</v>
+        <v>129476157</v>
       </c>
       <c r="B41" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381181</v>
+        <v>381464</v>
       </c>
       <c r="R41" t="n">
-        <v>6839245</v>
+        <v>6838872</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476157</v>
+        <v>129476151</v>
       </c>
       <c r="B42" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381464</v>
+        <v>381200</v>
       </c>
       <c r="R42" t="n">
-        <v>6838872</v>
+        <v>6839267</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476151</v>
+        <v>129476140</v>
       </c>
       <c r="B43" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381200</v>
+        <v>381382</v>
       </c>
       <c r="R43" t="n">
-        <v>6839267</v>
+        <v>6838962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,10 +5176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476140</v>
+        <v>129476144</v>
       </c>
       <c r="B44" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381382</v>
+        <v>381292</v>
       </c>
       <c r="R44" t="n">
-        <v>6838962</v>
+        <v>6838844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476144</v>
+        <v>129476127</v>
       </c>
       <c r="B45" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381292</v>
+        <v>381181</v>
       </c>
       <c r="R45" t="n">
-        <v>6838844</v>
+        <v>6839245</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5393,7 +5393,7 @@
         <v>129476142</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476143</v>
+        <v>129476174</v>
       </c>
       <c r="B47" t="n">
-        <v>78833</v>
+        <v>78479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381307</v>
+        <v>381317</v>
       </c>
       <c r="R47" t="n">
-        <v>6838866</v>
+        <v>6839120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476174</v>
+        <v>129476149</v>
       </c>
       <c r="B48" t="n">
-        <v>78478</v>
+        <v>78833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381317</v>
+        <v>381441</v>
       </c>
       <c r="R48" t="n">
-        <v>6839120</v>
+        <v>6838759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476149</v>
+        <v>129476143</v>
       </c>
       <c r="B49" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381441</v>
+        <v>381307</v>
       </c>
       <c r="R49" t="n">
-        <v>6838759</v>
+        <v>6838866</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5821,7 +5821,7 @@
         <v>129476164</v>
       </c>
       <c r="B50" t="n">
-        <v>79154</v>
+        <v>79155</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476171</v>
+        <v>129476138</v>
       </c>
       <c r="B51" t="n">
-        <v>78083</v>
+        <v>78834</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381283</v>
+        <v>381200</v>
       </c>
       <c r="R51" t="n">
-        <v>6838879</v>
+        <v>6839267</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476122</v>
+        <v>129476171</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>78084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>381350</v>
+        <v>381283</v>
       </c>
       <c r="R52" t="n">
-        <v>6838974</v>
+        <v>6838879</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476138</v>
+        <v>129476122</v>
       </c>
       <c r="B53" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381200</v>
+        <v>381350</v>
       </c>
       <c r="R53" t="n">
-        <v>6839267</v>
+        <v>6838974</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476166</v>
+        <v>129476163</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79155</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381368</v>
+        <v>381325</v>
       </c>
       <c r="R54" t="n">
-        <v>6838740</v>
+        <v>6838970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6356,7 +6356,7 @@
         <v>129476118</v>
       </c>
       <c r="B55" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476163</v>
+        <v>129476166</v>
       </c>
       <c r="B56" t="n">
-        <v>79154</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381325</v>
+        <v>381368</v>
       </c>
       <c r="R56" t="n">
-        <v>6838970</v>
+        <v>6838740</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,7 +6567,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476136</v>
+        <v>129476159</v>
       </c>
       <c r="B57" t="n">
         <v>78833</v>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381421</v>
+        <v>381360</v>
       </c>
       <c r="R57" t="n">
-        <v>6838767</v>
+        <v>6838853</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,10 +6674,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476155</v>
+        <v>129476136</v>
       </c>
       <c r="B58" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6685,21 +6685,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381382</v>
+        <v>381421</v>
       </c>
       <c r="R58" t="n">
-        <v>6838965</v>
+        <v>6838767</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476159</v>
+        <v>129476155</v>
       </c>
       <c r="B59" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R59" t="n">
-        <v>6838853</v>
+        <v>6838965</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476129</v>
+        <v>129476173</v>
       </c>
       <c r="B60" t="n">
-        <v>79665</v>
+        <v>78479</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6899,21 +6899,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>381313</v>
+        <v>381193</v>
       </c>
       <c r="R60" t="n">
-        <v>6839168</v>
+        <v>6839219</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6995,10 +6995,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476126</v>
+        <v>129476129</v>
       </c>
       <c r="B61" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381419</v>
+        <v>381313</v>
       </c>
       <c r="R61" t="n">
-        <v>6838773</v>
+        <v>6839168</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476139</v>
+        <v>129476126</v>
       </c>
       <c r="B62" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381291</v>
+        <v>381419</v>
       </c>
       <c r="R62" t="n">
-        <v>6839075</v>
+        <v>6838773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476173</v>
+        <v>129476139</v>
       </c>
       <c r="B63" t="n">
-        <v>78478</v>
+        <v>78834</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381193</v>
+        <v>381291</v>
       </c>
       <c r="R63" t="n">
-        <v>6839219</v>
+        <v>6839075</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B22" t="n">
-        <v>78834</v>
+        <v>78833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R22" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B23" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R23" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476156</v>
+        <v>129476131</v>
       </c>
       <c r="B25" t="n">
-        <v>78833</v>
+        <v>90620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381423</v>
+        <v>381232</v>
       </c>
       <c r="R25" t="n">
-        <v>6838921</v>
+        <v>6838826</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476131</v>
+        <v>129476156</v>
       </c>
       <c r="B26" t="n">
-        <v>90620</v>
+        <v>78833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381232</v>
+        <v>381423</v>
       </c>
       <c r="R26" t="n">
-        <v>6838826</v>
+        <v>6838921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476170</v>
+        <v>129476160</v>
       </c>
       <c r="B31" t="n">
-        <v>78084</v>
+        <v>78833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,21 +3787,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381444</v>
+        <v>381216</v>
       </c>
       <c r="R31" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476125</v>
+        <v>129476170</v>
       </c>
       <c r="B32" t="n">
-        <v>79666</v>
+        <v>78084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381441</v>
+        <v>381444</v>
       </c>
       <c r="R32" t="n">
         <v>6838763</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,7 +3990,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476130</v>
+        <v>129476125</v>
       </c>
       <c r="B33" t="n">
         <v>79666</v>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381290</v>
+        <v>381441</v>
       </c>
       <c r="R33" t="n">
-        <v>6839072</v>
+        <v>6838763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476160</v>
+        <v>129476130</v>
       </c>
       <c r="B34" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381216</v>
+        <v>381290</v>
       </c>
       <c r="R34" t="n">
-        <v>6838831</v>
+        <v>6839072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,32 +4204,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476167</v>
+        <v>129476147</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>57840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>381331</v>
+        <v>381339</v>
       </c>
       <c r="R35" t="n">
-        <v>6838974</v>
+        <v>6838869</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,32 +4311,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476147</v>
+        <v>129476167</v>
       </c>
       <c r="B36" t="n">
-        <v>57840</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>381339</v>
+        <v>381331</v>
       </c>
       <c r="R36" t="n">
-        <v>6838869</v>
+        <v>6838974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476157</v>
+        <v>129476140</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381464</v>
+        <v>381382</v>
       </c>
       <c r="R41" t="n">
-        <v>6838872</v>
+        <v>6838962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476151</v>
+        <v>129476144</v>
       </c>
       <c r="B42" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4973,21 +4973,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381200</v>
+        <v>381292</v>
       </c>
       <c r="R42" t="n">
-        <v>6839267</v>
+        <v>6838844</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476140</v>
+        <v>129476127</v>
       </c>
       <c r="B43" t="n">
-        <v>78834</v>
+        <v>79666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381382</v>
+        <v>381181</v>
       </c>
       <c r="R43" t="n">
-        <v>6838962</v>
+        <v>6839245</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,7 +5176,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476144</v>
+        <v>129476142</v>
       </c>
       <c r="B44" t="n">
         <v>78834</v>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381292</v>
+        <v>381360</v>
       </c>
       <c r="R44" t="n">
-        <v>6838844</v>
+        <v>6838853</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476127</v>
+        <v>129476157</v>
       </c>
       <c r="B45" t="n">
-        <v>79666</v>
+        <v>78833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381181</v>
+        <v>381464</v>
       </c>
       <c r="R45" t="n">
-        <v>6839245</v>
+        <v>6838872</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476142</v>
+        <v>129476151</v>
       </c>
       <c r="B46" t="n">
-        <v>78834</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381360</v>
+        <v>381200</v>
       </c>
       <c r="R46" t="n">
-        <v>6838853</v>
+        <v>6839267</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476163</v>
+        <v>129476166</v>
       </c>
       <c r="B54" t="n">
-        <v>79155</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381325</v>
+        <v>381368</v>
       </c>
       <c r="R54" t="n">
-        <v>6838970</v>
+        <v>6838740</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476118</v>
+        <v>129476163</v>
       </c>
       <c r="B55" t="n">
-        <v>79108</v>
+        <v>79155</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>381274</v>
+        <v>381325</v>
       </c>
       <c r="R55" t="n">
-        <v>6838892</v>
+        <v>6838970</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476166</v>
+        <v>129476118</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79108</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381368</v>
+        <v>381274</v>
       </c>
       <c r="R56" t="n">
-        <v>6838740</v>
+        <v>6838892</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1508,7 +1508,7 @@
         <v>129476135</v>
       </c>
       <c r="B10" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129476158</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476132</v>
+        <v>129476168</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,42 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381411</v>
+        <v>381310</v>
       </c>
       <c r="R12" t="n">
-        <v>6838786</v>
+        <v>6838877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1789,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1807,7 +1799,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476168</v>
+        <v>129476132</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,34 +1837,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381310</v>
+        <v>381411</v>
       </c>
       <c r="R13" t="n">
-        <v>6838877</v>
+        <v>6838786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1944,7 @@
         <v>129476123</v>
       </c>
       <c r="B14" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>129476120</v>
       </c>
       <c r="B15" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129476145</v>
       </c>
       <c r="B16" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476161</v>
+        <v>129476119</v>
       </c>
       <c r="B17" t="n">
-        <v>79155</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381371</v>
+        <v>381396</v>
       </c>
       <c r="R17" t="n">
-        <v>6838792</v>
+        <v>6838745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,24 +2351,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2385,32 +2369,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476162</v>
+        <v>129476169</v>
       </c>
       <c r="B18" t="n">
-        <v>79155</v>
+        <v>92875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381304</v>
+        <v>381326</v>
       </c>
       <c r="R18" t="n">
-        <v>6838862</v>
+        <v>6838973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2465,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476148</v>
+        <v>129476161</v>
       </c>
       <c r="B19" t="n">
-        <v>81061</v>
+        <v>79160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381218</v>
+        <v>381371</v>
       </c>
       <c r="R19" t="n">
-        <v>6838830</v>
+        <v>6838792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2546,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2556,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,8 +2565,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476169</v>
+        <v>129476148</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>81066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381326</v>
+        <v>381218</v>
       </c>
       <c r="R20" t="n">
-        <v>6838973</v>
+        <v>6838830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476119</v>
+        <v>129476162</v>
       </c>
       <c r="B21" t="n">
-        <v>79695</v>
+        <v>79160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381396</v>
+        <v>381304</v>
       </c>
       <c r="R21" t="n">
-        <v>6838745</v>
+        <v>6838862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2816,7 +2816,7 @@
         <v>129476154</v>
       </c>
       <c r="B22" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129476141</v>
       </c>
       <c r="B23" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476150</v>
+        <v>129476131</v>
       </c>
       <c r="B24" t="n">
-        <v>78833</v>
+        <v>90625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381228</v>
+        <v>381232</v>
       </c>
       <c r="R24" t="n">
-        <v>6838960</v>
+        <v>6838826</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476131</v>
+        <v>129476150</v>
       </c>
       <c r="B25" t="n">
-        <v>90620</v>
+        <v>78838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381232</v>
+        <v>381228</v>
       </c>
       <c r="R25" t="n">
-        <v>6838826</v>
+        <v>6838960</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,7 +3244,7 @@
         <v>129476156</v>
       </c>
       <c r="B26" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129476124</v>
       </c>
       <c r="B27" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>129476137</v>
       </c>
       <c r="B28" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129476172</v>
       </c>
       <c r="B29" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129476153</v>
       </c>
       <c r="B30" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476160</v>
+        <v>129476170</v>
       </c>
       <c r="B31" t="n">
-        <v>78833</v>
+        <v>78089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,21 +3787,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381216</v>
+        <v>381444</v>
       </c>
       <c r="R31" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476170</v>
+        <v>129476160</v>
       </c>
       <c r="B32" t="n">
-        <v>78084</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381444</v>
+        <v>381216</v>
       </c>
       <c r="R32" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3993,7 +3993,7 @@
         <v>129476125</v>
       </c>
       <c r="B33" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>129476130</v>
       </c>
       <c r="B34" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>129476167</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476133</v>
+        <v>129476121</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,42 +4429,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381329</v>
+        <v>381322</v>
       </c>
       <c r="R37" t="n">
-        <v>6838937</v>
+        <v>6839022</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4506,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476128</v>
+        <v>129476133</v>
       </c>
       <c r="B38" t="n">
-        <v>79666</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4544,34 +4536,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>381183</v>
+        <v>381329</v>
       </c>
       <c r="R38" t="n">
-        <v>6839285</v>
+        <v>6838937</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476121</v>
+        <v>129476128</v>
       </c>
       <c r="B39" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381322</v>
+        <v>381183</v>
       </c>
       <c r="R39" t="n">
-        <v>6839022</v>
+        <v>6839285</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4747,32 +4747,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476146</v>
+        <v>129476157</v>
       </c>
       <c r="B40" t="n">
-        <v>91876</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>381251</v>
+        <v>381464</v>
       </c>
       <c r="R40" t="n">
-        <v>6839071</v>
+        <v>6838872</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4836,7 +4836,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4855,10 +4854,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476140</v>
+        <v>129476151</v>
       </c>
       <c r="B41" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4865,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4889,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381382</v>
+        <v>381200</v>
       </c>
       <c r="R41" t="n">
-        <v>6838962</v>
+        <v>6839267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4924,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4934,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,32 +4961,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476144</v>
+        <v>129476146</v>
       </c>
       <c r="B42" t="n">
-        <v>78834</v>
+        <v>91881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>71</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4996,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381292</v>
+        <v>381251</v>
       </c>
       <c r="R42" t="n">
-        <v>6838844</v>
+        <v>6839071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5031,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5041,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5051,6 +5050,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476127</v>
+        <v>129476140</v>
       </c>
       <c r="B43" t="n">
-        <v>79666</v>
+        <v>78839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381181</v>
+        <v>381382</v>
       </c>
       <c r="R43" t="n">
-        <v>6839245</v>
+        <v>6838962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,10 +5176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476142</v>
+        <v>129476144</v>
       </c>
       <c r="B44" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381360</v>
+        <v>381292</v>
       </c>
       <c r="R44" t="n">
-        <v>6838853</v>
+        <v>6838844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476157</v>
+        <v>129476127</v>
       </c>
       <c r="B45" t="n">
-        <v>78833</v>
+        <v>79671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381464</v>
+        <v>381181</v>
       </c>
       <c r="R45" t="n">
-        <v>6838872</v>
+        <v>6839245</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476151</v>
+        <v>129476142</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381200</v>
+        <v>381360</v>
       </c>
       <c r="R46" t="n">
-        <v>6839267</v>
+        <v>6838853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5500,7 +5500,7 @@
         <v>129476174</v>
       </c>
       <c r="B47" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>129476149</v>
       </c>
       <c r="B48" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>129476143</v>
       </c>
       <c r="B49" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476164</v>
+        <v>129476138</v>
       </c>
       <c r="B50" t="n">
-        <v>79155</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381410</v>
+        <v>381200</v>
       </c>
       <c r="R50" t="n">
-        <v>6838936</v>
+        <v>6839267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476138</v>
+        <v>129476164</v>
       </c>
       <c r="B51" t="n">
-        <v>78834</v>
+        <v>79160</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381200</v>
+        <v>381410</v>
       </c>
       <c r="R51" t="n">
-        <v>6839267</v>
+        <v>6838936</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6035,7 +6035,7 @@
         <v>129476171</v>
       </c>
       <c r="B52" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>129476122</v>
       </c>
       <c r="B53" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>129476166</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476163</v>
+        <v>129476118</v>
       </c>
       <c r="B55" t="n">
-        <v>79155</v>
+        <v>79113</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>381325</v>
+        <v>381274</v>
       </c>
       <c r="R55" t="n">
-        <v>6838970</v>
+        <v>6838892</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476118</v>
+        <v>129476163</v>
       </c>
       <c r="B56" t="n">
-        <v>79108</v>
+        <v>79160</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381274</v>
+        <v>381325</v>
       </c>
       <c r="R56" t="n">
-        <v>6838892</v>
+        <v>6838970</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476159</v>
+        <v>129476136</v>
       </c>
       <c r="B57" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381360</v>
+        <v>381421</v>
       </c>
       <c r="R57" t="n">
-        <v>6838853</v>
+        <v>6838767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,10 +6674,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476136</v>
+        <v>129476155</v>
       </c>
       <c r="B58" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6685,21 +6685,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381421</v>
+        <v>381382</v>
       </c>
       <c r="R58" t="n">
-        <v>6838767</v>
+        <v>6838965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476155</v>
+        <v>129476159</v>
       </c>
       <c r="B59" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R59" t="n">
-        <v>6838965</v>
+        <v>6838853</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476173</v>
+        <v>129476129</v>
       </c>
       <c r="B60" t="n">
-        <v>78479</v>
+        <v>79671</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6899,21 +6899,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>381193</v>
+        <v>381313</v>
       </c>
       <c r="R60" t="n">
-        <v>6839219</v>
+        <v>6839168</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6995,10 +6995,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476129</v>
+        <v>129476126</v>
       </c>
       <c r="B61" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381313</v>
+        <v>381419</v>
       </c>
       <c r="R61" t="n">
-        <v>6839168</v>
+        <v>6838773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476126</v>
+        <v>129476139</v>
       </c>
       <c r="B62" t="n">
-        <v>79666</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381419</v>
+        <v>381291</v>
       </c>
       <c r="R62" t="n">
-        <v>6838773</v>
+        <v>6839075</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476139</v>
+        <v>129476173</v>
       </c>
       <c r="B63" t="n">
-        <v>78834</v>
+        <v>78484</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381291</v>
+        <v>381193</v>
       </c>
       <c r="R63" t="n">
-        <v>6839075</v>
+        <v>6839219</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476168</v>
+        <v>129476123</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381310</v>
+        <v>381425</v>
       </c>
       <c r="R12" t="n">
-        <v>6838877</v>
+        <v>6838921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476123</v>
+        <v>129476168</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>381425</v>
+        <v>381310</v>
       </c>
       <c r="R14" t="n">
-        <v>6838921</v>
+        <v>6838877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476119</v>
+        <v>129476169</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381396</v>
+        <v>381326</v>
       </c>
       <c r="R17" t="n">
-        <v>6838745</v>
+        <v>6838973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,32 +2369,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476169</v>
+        <v>129476161</v>
       </c>
       <c r="B18" t="n">
-        <v>92875</v>
+        <v>79160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381326</v>
+        <v>381371</v>
       </c>
       <c r="R18" t="n">
-        <v>6838973</v>
+        <v>6838792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,8 +2458,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2476,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476161</v>
+        <v>129476148</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>81066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381371</v>
+        <v>381218</v>
       </c>
       <c r="R19" t="n">
-        <v>6838792</v>
+        <v>6838830</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2556,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2565,24 +2581,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476148</v>
+        <v>129476119</v>
       </c>
       <c r="B20" t="n">
-        <v>81066</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381218</v>
+        <v>381396</v>
       </c>
       <c r="R20" t="n">
-        <v>6838830</v>
+        <v>6838745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3134,7 +3134,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476150</v>
+        <v>129476156</v>
       </c>
       <c r="B25" t="n">
         <v>78838</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381228</v>
+        <v>381423</v>
       </c>
       <c r="R25" t="n">
-        <v>6838960</v>
+        <v>6838921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,7 +3241,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476156</v>
+        <v>129476150</v>
       </c>
       <c r="B26" t="n">
         <v>78838</v>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381423</v>
+        <v>381228</v>
       </c>
       <c r="R26" t="n">
-        <v>6838921</v>
+        <v>6838960</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476170</v>
+        <v>129476130</v>
       </c>
       <c r="B31" t="n">
-        <v>78089</v>
+        <v>79671</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,21 +3787,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381444</v>
+        <v>381290</v>
       </c>
       <c r="R31" t="n">
-        <v>6838763</v>
+        <v>6839072</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476160</v>
+        <v>129476125</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381216</v>
+        <v>381441</v>
       </c>
       <c r="R32" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476125</v>
+        <v>129476160</v>
       </c>
       <c r="B33" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381441</v>
+        <v>381216</v>
       </c>
       <c r="R33" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476130</v>
+        <v>129476170</v>
       </c>
       <c r="B34" t="n">
-        <v>79671</v>
+        <v>78089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381290</v>
+        <v>381444</v>
       </c>
       <c r="R34" t="n">
-        <v>6839072</v>
+        <v>6838763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,32 +4204,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476147</v>
+        <v>129476167</v>
       </c>
       <c r="B35" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>381339</v>
+        <v>381331</v>
       </c>
       <c r="R35" t="n">
-        <v>6838869</v>
+        <v>6838974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,32 +4311,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476167</v>
+        <v>129476147</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>381331</v>
+        <v>381339</v>
       </c>
       <c r="R36" t="n">
-        <v>6838974</v>
+        <v>6838869</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476157</v>
+        <v>129476140</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4758,21 +4758,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>381464</v>
+        <v>381382</v>
       </c>
       <c r="R40" t="n">
-        <v>6838872</v>
+        <v>6838962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476151</v>
+        <v>129476144</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381200</v>
+        <v>381292</v>
       </c>
       <c r="R41" t="n">
-        <v>6839267</v>
+        <v>6838844</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4961,32 +4961,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476146</v>
+        <v>129476127</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>79671</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381251</v>
+        <v>381181</v>
       </c>
       <c r="R42" t="n">
-        <v>6839071</v>
+        <v>6839245</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5050,7 +5050,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5069,7 +5068,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476140</v>
+        <v>129476142</v>
       </c>
       <c r="B43" t="n">
         <v>78839</v>
@@ -5104,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R43" t="n">
-        <v>6838962</v>
+        <v>6838853</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5138,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5148,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,10 +5175,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476144</v>
+        <v>129476157</v>
       </c>
       <c r="B44" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5187,21 +5186,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5211,10 +5210,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381292</v>
+        <v>381464</v>
       </c>
       <c r="R44" t="n">
-        <v>6838844</v>
+        <v>6838872</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5245,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5282,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476127</v>
+        <v>129476151</v>
       </c>
       <c r="B45" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5293,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5317,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381181</v>
+        <v>381200</v>
       </c>
       <c r="R45" t="n">
-        <v>6839245</v>
+        <v>6839267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5352,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5362,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,32 +5389,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476142</v>
+        <v>129476146</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>91881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>71</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5424,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381360</v>
+        <v>381251</v>
       </c>
       <c r="R46" t="n">
-        <v>6838853</v>
+        <v>6839071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5459,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5469,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5479,6 +5478,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476174</v>
+        <v>129476143</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381317</v>
+        <v>381307</v>
       </c>
       <c r="R47" t="n">
-        <v>6839120</v>
+        <v>6838866</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476149</v>
+        <v>129476174</v>
       </c>
       <c r="B48" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381441</v>
+        <v>381317</v>
       </c>
       <c r="R48" t="n">
-        <v>6838759</v>
+        <v>6839120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476143</v>
+        <v>129476149</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381307</v>
+        <v>381441</v>
       </c>
       <c r="R49" t="n">
-        <v>6838866</v>
+        <v>6838759</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476138</v>
+        <v>129476164</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>79160</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381200</v>
+        <v>381410</v>
       </c>
       <c r="R50" t="n">
-        <v>6839267</v>
+        <v>6838936</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476164</v>
+        <v>129476122</v>
       </c>
       <c r="B51" t="n">
-        <v>79160</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381410</v>
+        <v>381350</v>
       </c>
       <c r="R51" t="n">
-        <v>6838936</v>
+        <v>6838974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476122</v>
+        <v>129476138</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381350</v>
+        <v>381200</v>
       </c>
       <c r="R53" t="n">
-        <v>6838974</v>
+        <v>6839267</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476166</v>
+        <v>129476163</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381368</v>
+        <v>381325</v>
       </c>
       <c r="R54" t="n">
-        <v>6838740</v>
+        <v>6838970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476118</v>
+        <v>129476166</v>
       </c>
       <c r="B55" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>381274</v>
+        <v>381368</v>
       </c>
       <c r="R55" t="n">
-        <v>6838892</v>
+        <v>6838740</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476163</v>
+        <v>129476118</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>79113</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381325</v>
+        <v>381274</v>
       </c>
       <c r="R56" t="n">
-        <v>6838970</v>
+        <v>6838892</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476136</v>
+        <v>129476155</v>
       </c>
       <c r="B57" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381421</v>
+        <v>381382</v>
       </c>
       <c r="R57" t="n">
-        <v>6838767</v>
+        <v>6838965</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,7 +6674,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476155</v>
+        <v>129476159</v>
       </c>
       <c r="B58" t="n">
         <v>78838</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R58" t="n">
-        <v>6838965</v>
+        <v>6838853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476159</v>
+        <v>129476136</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381360</v>
+        <v>381421</v>
       </c>
       <c r="R59" t="n">
-        <v>6838853</v>
+        <v>6838767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476123</v>
+        <v>129476132</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381425</v>
+        <v>381411</v>
       </c>
       <c r="R12" t="n">
-        <v>6838921</v>
+        <v>6838786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1797,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1799,7 +1807,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476132</v>
+        <v>129476123</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,42 +1845,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381411</v>
+        <v>381425</v>
       </c>
       <c r="R13" t="n">
-        <v>6838786</v>
+        <v>6838921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476169</v>
+        <v>129476148</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>81066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381326</v>
+        <v>381218</v>
       </c>
       <c r="R17" t="n">
-        <v>6838973</v>
+        <v>6838830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476148</v>
+        <v>129476162</v>
       </c>
       <c r="B19" t="n">
-        <v>81066</v>
+        <v>79160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381218</v>
+        <v>381304</v>
       </c>
       <c r="R19" t="n">
-        <v>6838830</v>
+        <v>6838862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476119</v>
+        <v>129476169</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381396</v>
+        <v>381326</v>
       </c>
       <c r="R20" t="n">
-        <v>6838745</v>
+        <v>6838973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476162</v>
+        <v>129476119</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381304</v>
+        <v>381396</v>
       </c>
       <c r="R21" t="n">
-        <v>6838862</v>
+        <v>6838745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R22" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R23" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,7 +3134,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476156</v>
+        <v>129476150</v>
       </c>
       <c r="B25" t="n">
         <v>78838</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381423</v>
+        <v>381228</v>
       </c>
       <c r="R25" t="n">
-        <v>6838921</v>
+        <v>6838960</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,7 +3241,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476150</v>
+        <v>129476156</v>
       </c>
       <c r="B26" t="n">
         <v>78838</v>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381228</v>
+        <v>381423</v>
       </c>
       <c r="R26" t="n">
-        <v>6838960</v>
+        <v>6838921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3776,7 +3776,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476130</v>
+        <v>129476125</v>
       </c>
       <c r="B31" t="n">
         <v>79671</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381290</v>
+        <v>381441</v>
       </c>
       <c r="R31" t="n">
-        <v>6839072</v>
+        <v>6838763</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476125</v>
+        <v>129476130</v>
       </c>
       <c r="B32" t="n">
         <v>79671</v>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381441</v>
+        <v>381290</v>
       </c>
       <c r="R32" t="n">
-        <v>6838763</v>
+        <v>6839072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476160</v>
+        <v>129476170</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>78089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381216</v>
+        <v>381444</v>
       </c>
       <c r="R33" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476170</v>
+        <v>129476160</v>
       </c>
       <c r="B34" t="n">
-        <v>78089</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381444</v>
+        <v>381216</v>
       </c>
       <c r="R34" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476121</v>
+        <v>129476128</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381322</v>
+        <v>381183</v>
       </c>
       <c r="R37" t="n">
-        <v>6839022</v>
+        <v>6839285</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4640,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476128</v>
+        <v>129476121</v>
       </c>
       <c r="B39" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381183</v>
+        <v>381322</v>
       </c>
       <c r="R39" t="n">
-        <v>6839285</v>
+        <v>6839022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5175,32 +5175,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476157</v>
+        <v>129476146</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>91881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>71</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381464</v>
+        <v>381251</v>
       </c>
       <c r="R44" t="n">
-        <v>6838872</v>
+        <v>6839071</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5264,6 +5264,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5282,7 +5283,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476151</v>
+        <v>129476157</v>
       </c>
       <c r="B45" t="n">
         <v>78838</v>
@@ -5317,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381200</v>
+        <v>381464</v>
       </c>
       <c r="R45" t="n">
-        <v>6839267</v>
+        <v>6838872</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5352,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5362,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5389,32 +5390,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476146</v>
+        <v>129476151</v>
       </c>
       <c r="B46" t="n">
-        <v>91881</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5424,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381251</v>
+        <v>381200</v>
       </c>
       <c r="R46" t="n">
-        <v>6839071</v>
+        <v>6839267</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5459,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5469,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,7 +5479,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476143</v>
+        <v>129476149</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381307</v>
+        <v>381441</v>
       </c>
       <c r="R47" t="n">
-        <v>6838866</v>
+        <v>6838759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476174</v>
+        <v>129476143</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381317</v>
+        <v>381307</v>
       </c>
       <c r="R48" t="n">
-        <v>6839120</v>
+        <v>6838866</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476149</v>
+        <v>129476174</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381441</v>
+        <v>381317</v>
       </c>
       <c r="R49" t="n">
-        <v>6838759</v>
+        <v>6839120</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476163</v>
+        <v>129476118</v>
       </c>
       <c r="B54" t="n">
-        <v>79160</v>
+        <v>79113</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381325</v>
+        <v>381274</v>
       </c>
       <c r="R54" t="n">
-        <v>6838970</v>
+        <v>6838892</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476118</v>
+        <v>129476163</v>
       </c>
       <c r="B56" t="n">
-        <v>79113</v>
+        <v>79160</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381274</v>
+        <v>381325</v>
       </c>
       <c r="R56" t="n">
-        <v>6838892</v>
+        <v>6838970</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476129</v>
+        <v>129476173</v>
       </c>
       <c r="B60" t="n">
-        <v>79671</v>
+        <v>78484</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6899,21 +6899,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>381313</v>
+        <v>381193</v>
       </c>
       <c r="R60" t="n">
-        <v>6839168</v>
+        <v>6839219</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476126</v>
+        <v>129476129</v>
       </c>
       <c r="B61" t="n">
         <v>79671</v>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381419</v>
+        <v>381313</v>
       </c>
       <c r="R61" t="n">
-        <v>6838773</v>
+        <v>6839168</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476139</v>
+        <v>129476126</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381291</v>
+        <v>381419</v>
       </c>
       <c r="R62" t="n">
-        <v>6839075</v>
+        <v>6838773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476173</v>
+        <v>129476139</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381193</v>
+        <v>381291</v>
       </c>
       <c r="R63" t="n">
-        <v>6839219</v>
+        <v>6839075</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476132</v>
+        <v>129476168</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,42 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381411</v>
+        <v>381310</v>
       </c>
       <c r="R12" t="n">
-        <v>6838786</v>
+        <v>6838877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1789,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1807,7 +1799,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476123</v>
+        <v>129476132</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,34 +1837,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381425</v>
+        <v>381411</v>
       </c>
       <c r="R13" t="n">
-        <v>6838921</v>
+        <v>6838786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476168</v>
+        <v>129476123</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>381310</v>
+        <v>381425</v>
       </c>
       <c r="R14" t="n">
-        <v>6838877</v>
+        <v>6838921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476148</v>
+        <v>129476169</v>
       </c>
       <c r="B17" t="n">
-        <v>81066</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381218</v>
+        <v>381326</v>
       </c>
       <c r="R17" t="n">
-        <v>6838830</v>
+        <v>6838973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,7 +2369,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476161</v>
+        <v>129476162</v>
       </c>
       <c r="B18" t="n">
         <v>79160</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381371</v>
+        <v>381304</v>
       </c>
       <c r="R18" t="n">
-        <v>6838792</v>
+        <v>6838862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,24 +2458,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2492,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476162</v>
+        <v>129476119</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381304</v>
+        <v>381396</v>
       </c>
       <c r="R19" t="n">
-        <v>6838862</v>
+        <v>6838745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2546,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2556,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,32 +2583,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476169</v>
+        <v>129476161</v>
       </c>
       <c r="B20" t="n">
-        <v>92875</v>
+        <v>79160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381326</v>
+        <v>381371</v>
       </c>
       <c r="R20" t="n">
-        <v>6838973</v>
+        <v>6838792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2653,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2663,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,8 +2672,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476119</v>
+        <v>129476148</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>81066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381396</v>
+        <v>381218</v>
       </c>
       <c r="R21" t="n">
-        <v>6838745</v>
+        <v>6838830</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R22" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R23" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476170</v>
+        <v>129476160</v>
       </c>
       <c r="B33" t="n">
-        <v>78089</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381444</v>
+        <v>381216</v>
       </c>
       <c r="R33" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476160</v>
+        <v>129476170</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>78089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381216</v>
+        <v>381444</v>
       </c>
       <c r="R34" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476128</v>
+        <v>129476121</v>
       </c>
       <c r="B37" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381183</v>
+        <v>381322</v>
       </c>
       <c r="R37" t="n">
-        <v>6839285</v>
+        <v>6839022</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4640,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476121</v>
+        <v>129476128</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381322</v>
+        <v>381183</v>
       </c>
       <c r="R39" t="n">
-        <v>6839022</v>
+        <v>6839285</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4747,32 +4747,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476140</v>
+        <v>129476146</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>91881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>71</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>381382</v>
+        <v>381251</v>
       </c>
       <c r="R40" t="n">
-        <v>6838962</v>
+        <v>6839071</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4836,6 +4836,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4854,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476144</v>
+        <v>129476157</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4865,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4889,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381292</v>
+        <v>381464</v>
       </c>
       <c r="R41" t="n">
-        <v>6838844</v>
+        <v>6838872</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4924,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4934,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4961,10 +4962,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476127</v>
+        <v>129476151</v>
       </c>
       <c r="B42" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4972,21 +4973,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4996,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381181</v>
+        <v>381200</v>
       </c>
       <c r="R42" t="n">
-        <v>6839245</v>
+        <v>6839267</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5031,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5041,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5068,7 +5069,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476142</v>
+        <v>129476140</v>
       </c>
       <c r="B43" t="n">
         <v>78839</v>
@@ -5103,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R43" t="n">
-        <v>6838853</v>
+        <v>6838962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5138,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5148,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5175,32 +5176,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476146</v>
+        <v>129476144</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>78839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>71</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5210,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381251</v>
+        <v>381292</v>
       </c>
       <c r="R44" t="n">
-        <v>6839071</v>
+        <v>6838844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5245,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5255,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5264,7 +5265,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476157</v>
+        <v>129476127</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381464</v>
+        <v>381181</v>
       </c>
       <c r="R45" t="n">
-        <v>6838872</v>
+        <v>6839245</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476151</v>
+        <v>129476142</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381200</v>
+        <v>381360</v>
       </c>
       <c r="R46" t="n">
-        <v>6839267</v>
+        <v>6838853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476149</v>
+        <v>129476174</v>
       </c>
       <c r="B47" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381441</v>
+        <v>381317</v>
       </c>
       <c r="R47" t="n">
-        <v>6838759</v>
+        <v>6839120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476143</v>
+        <v>129476149</v>
       </c>
       <c r="B48" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381307</v>
+        <v>381441</v>
       </c>
       <c r="R48" t="n">
-        <v>6838866</v>
+        <v>6838759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476174</v>
+        <v>129476143</v>
       </c>
       <c r="B49" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381317</v>
+        <v>381307</v>
       </c>
       <c r="R49" t="n">
-        <v>6839120</v>
+        <v>6838866</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476164</v>
+        <v>129476138</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381410</v>
+        <v>381200</v>
       </c>
       <c r="R50" t="n">
-        <v>6838936</v>
+        <v>6839267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476122</v>
+        <v>129476164</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79160</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381350</v>
+        <v>381410</v>
       </c>
       <c r="R51" t="n">
-        <v>6838974</v>
+        <v>6838936</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476138</v>
+        <v>129476122</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381200</v>
+        <v>381350</v>
       </c>
       <c r="R53" t="n">
-        <v>6839267</v>
+        <v>6838974</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476118</v>
+        <v>129476163</v>
       </c>
       <c r="B54" t="n">
-        <v>79113</v>
+        <v>79160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381274</v>
+        <v>381325</v>
       </c>
       <c r="R54" t="n">
-        <v>6838892</v>
+        <v>6838970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476166</v>
+        <v>129476118</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>381368</v>
+        <v>381274</v>
       </c>
       <c r="R55" t="n">
-        <v>6838740</v>
+        <v>6838892</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6460,10 +6460,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476163</v>
+        <v>129476166</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6471,21 +6471,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381325</v>
+        <v>381368</v>
       </c>
       <c r="R56" t="n">
-        <v>6838970</v>
+        <v>6838740</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,7 +6567,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476155</v>
+        <v>129476159</v>
       </c>
       <c r="B57" t="n">
         <v>78838</v>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R57" t="n">
-        <v>6838965</v>
+        <v>6838853</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,7 +6674,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476159</v>
+        <v>129476155</v>
       </c>
       <c r="B58" t="n">
         <v>78838</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R58" t="n">
-        <v>6838853</v>
+        <v>6838965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476168</v>
+        <v>129476132</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1730,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381310</v>
+        <v>381411</v>
       </c>
       <c r="R12" t="n">
-        <v>6838877</v>
+        <v>6838786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1797,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1799,7 +1807,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476132</v>
+        <v>129476168</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,42 +1845,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381411</v>
+        <v>381310</v>
       </c>
       <c r="R13" t="n">
-        <v>6838786</v>
+        <v>6838877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476169</v>
+        <v>129476119</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381326</v>
+        <v>381396</v>
       </c>
       <c r="R17" t="n">
-        <v>6838973</v>
+        <v>6838745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,32 +2369,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476162</v>
+        <v>129476169</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>92879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381304</v>
+        <v>381326</v>
       </c>
       <c r="R18" t="n">
-        <v>6838862</v>
+        <v>6838973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476119</v>
+        <v>129476161</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381396</v>
+        <v>381371</v>
       </c>
       <c r="R19" t="n">
-        <v>6838745</v>
+        <v>6838792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2565,8 +2565,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2583,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476161</v>
+        <v>129476148</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>81066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381371</v>
+        <v>381218</v>
       </c>
       <c r="R20" t="n">
-        <v>6838792</v>
+        <v>6838830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2663,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2672,24 +2688,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476148</v>
+        <v>129476162</v>
       </c>
       <c r="B21" t="n">
-        <v>81066</v>
+        <v>79160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381218</v>
+        <v>381304</v>
       </c>
       <c r="R21" t="n">
-        <v>6838830</v>
+        <v>6838862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R22" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R23" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476131</v>
+        <v>129476156</v>
       </c>
       <c r="B24" t="n">
-        <v>90625</v>
+        <v>78838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381232</v>
+        <v>381423</v>
       </c>
       <c r="R24" t="n">
-        <v>6838826</v>
+        <v>6838921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476156</v>
+        <v>129476131</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>90629</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381423</v>
+        <v>381232</v>
       </c>
       <c r="R26" t="n">
-        <v>6838921</v>
+        <v>6838826</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476172</v>
+        <v>129476153</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>78838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>381438</v>
+        <v>381291</v>
       </c>
       <c r="R29" t="n">
-        <v>6838768</v>
+        <v>6839075</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476153</v>
+        <v>129476172</v>
       </c>
       <c r="B30" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>381291</v>
+        <v>381438</v>
       </c>
       <c r="R30" t="n">
-        <v>6839075</v>
+        <v>6838768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476160</v>
+        <v>129476170</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>78089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381216</v>
+        <v>381444</v>
       </c>
       <c r="R33" t="n">
-        <v>6838831</v>
+        <v>6838763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476170</v>
+        <v>129476160</v>
       </c>
       <c r="B34" t="n">
-        <v>78089</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381444</v>
+        <v>381216</v>
       </c>
       <c r="R34" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4750,7 +4750,7 @@
         <v>129476146</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>91885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476157</v>
+        <v>129476151</v>
       </c>
       <c r="B41" t="n">
         <v>78838</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381464</v>
+        <v>381200</v>
       </c>
       <c r="R41" t="n">
-        <v>6838872</v>
+        <v>6839267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,7 +4962,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476151</v>
+        <v>129476157</v>
       </c>
       <c r="B42" t="n">
         <v>78838</v>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381200</v>
+        <v>381464</v>
       </c>
       <c r="R42" t="n">
-        <v>6839267</v>
+        <v>6838872</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476138</v>
+        <v>129476164</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>79160</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381200</v>
+        <v>381410</v>
       </c>
       <c r="R50" t="n">
-        <v>6839267</v>
+        <v>6838936</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476164</v>
+        <v>129476171</v>
       </c>
       <c r="B51" t="n">
-        <v>79160</v>
+        <v>78089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381410</v>
+        <v>381283</v>
       </c>
       <c r="R51" t="n">
-        <v>6838936</v>
+        <v>6838879</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476171</v>
+        <v>129476122</v>
       </c>
       <c r="B52" t="n">
-        <v>78089</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>381283</v>
+        <v>381350</v>
       </c>
       <c r="R52" t="n">
-        <v>6838879</v>
+        <v>6838974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476122</v>
+        <v>129476138</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381350</v>
+        <v>381200</v>
       </c>
       <c r="R53" t="n">
-        <v>6838974</v>
+        <v>6839267</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476163</v>
+        <v>129476118</v>
       </c>
       <c r="B54" t="n">
-        <v>79160</v>
+        <v>79113</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>381325</v>
+        <v>381274</v>
       </c>
       <c r="R54" t="n">
-        <v>6838970</v>
+        <v>6838892</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476118</v>
+        <v>129476163</v>
       </c>
       <c r="B55" t="n">
-        <v>79113</v>
+        <v>79160</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>381274</v>
+        <v>381325</v>
       </c>
       <c r="R55" t="n">
-        <v>6838892</v>
+        <v>6838970</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6567,7 +6567,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476159</v>
+        <v>129476155</v>
       </c>
       <c r="B57" t="n">
         <v>78838</v>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R57" t="n">
-        <v>6838853</v>
+        <v>6838965</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,7 +6674,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476155</v>
+        <v>129476159</v>
       </c>
       <c r="B58" t="n">
         <v>78838</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R58" t="n">
-        <v>6838965</v>
+        <v>6838853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476119</v>
+        <v>129476169</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381396</v>
+        <v>381326</v>
       </c>
       <c r="R17" t="n">
-        <v>6838745</v>
+        <v>6838973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,32 +2369,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476169</v>
+        <v>129476161</v>
       </c>
       <c r="B18" t="n">
-        <v>92879</v>
+        <v>79160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381326</v>
+        <v>381371</v>
       </c>
       <c r="R18" t="n">
-        <v>6838973</v>
+        <v>6838792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,8 +2458,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2476,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476161</v>
+        <v>129476148</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>81066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381371</v>
+        <v>381218</v>
       </c>
       <c r="R19" t="n">
-        <v>6838792</v>
+        <v>6838830</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2556,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2565,24 +2581,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476148</v>
+        <v>129476162</v>
       </c>
       <c r="B20" t="n">
-        <v>81066</v>
+        <v>79160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381218</v>
+        <v>381304</v>
       </c>
       <c r="R20" t="n">
-        <v>6838830</v>
+        <v>6838862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476162</v>
+        <v>129476119</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>381304</v>
+        <v>381396</v>
       </c>
       <c r="R21" t="n">
-        <v>6838862</v>
+        <v>6838745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476156</v>
+        <v>129476131</v>
       </c>
       <c r="B24" t="n">
-        <v>78838</v>
+        <v>90631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381423</v>
+        <v>381232</v>
       </c>
       <c r="R24" t="n">
-        <v>6838921</v>
+        <v>6838826</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476131</v>
+        <v>129476156</v>
       </c>
       <c r="B26" t="n">
-        <v>90629</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381232</v>
+        <v>381423</v>
       </c>
       <c r="R26" t="n">
-        <v>6838826</v>
+        <v>6838921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476153</v>
+        <v>129476172</v>
       </c>
       <c r="B29" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>381291</v>
+        <v>381438</v>
       </c>
       <c r="R29" t="n">
-        <v>6839075</v>
+        <v>6838768</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476172</v>
+        <v>129476153</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>78838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>381438</v>
+        <v>381291</v>
       </c>
       <c r="R30" t="n">
-        <v>6838768</v>
+        <v>6839075</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476125</v>
+        <v>129476160</v>
       </c>
       <c r="B31" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,21 +3787,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381441</v>
+        <v>381216</v>
       </c>
       <c r="R31" t="n">
-        <v>6838763</v>
+        <v>6838831</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129476130</v>
+        <v>129476170</v>
       </c>
       <c r="B32" t="n">
-        <v>79671</v>
+        <v>78089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381290</v>
+        <v>381444</v>
       </c>
       <c r="R32" t="n">
-        <v>6839072</v>
+        <v>6838763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476170</v>
+        <v>129476125</v>
       </c>
       <c r="B33" t="n">
-        <v>78089</v>
+        <v>79671</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381444</v>
+        <v>381441</v>
       </c>
       <c r="R33" t="n">
         <v>6838763</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476160</v>
+        <v>129476130</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381216</v>
+        <v>381290</v>
       </c>
       <c r="R34" t="n">
-        <v>6838831</v>
+        <v>6839072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4204,32 +4204,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129476167</v>
+        <v>129476147</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>381331</v>
+        <v>381339</v>
       </c>
       <c r="R35" t="n">
-        <v>6838974</v>
+        <v>6838869</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4311,32 +4311,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476147</v>
+        <v>129476167</v>
       </c>
       <c r="B36" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>381339</v>
+        <v>381331</v>
       </c>
       <c r="R36" t="n">
-        <v>6838869</v>
+        <v>6838974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476121</v>
+        <v>129476128</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381322</v>
+        <v>381183</v>
       </c>
       <c r="R37" t="n">
-        <v>6839022</v>
+        <v>6839285</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476133</v>
+        <v>129476121</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,42 +4536,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>381329</v>
+        <v>381322</v>
       </c>
       <c r="R38" t="n">
-        <v>6838937</v>
+        <v>6839022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4613,7 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4632,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476128</v>
+        <v>129476133</v>
       </c>
       <c r="B39" t="n">
-        <v>79671</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,34 +4643,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nordväst Stenvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381183</v>
+        <v>381329</v>
       </c>
       <c r="R39" t="n">
-        <v>6839285</v>
+        <v>6838937</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4750,7 +4750,7 @@
         <v>129476146</v>
       </c>
       <c r="B40" t="n">
-        <v>91885</v>
+        <v>91887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476151</v>
+        <v>129476140</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381200</v>
+        <v>381382</v>
       </c>
       <c r="R41" t="n">
-        <v>6839267</v>
+        <v>6838962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476157</v>
+        <v>129476144</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4973,21 +4973,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381464</v>
+        <v>381292</v>
       </c>
       <c r="R42" t="n">
-        <v>6838872</v>
+        <v>6838844</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476140</v>
+        <v>129476127</v>
       </c>
       <c r="B43" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381382</v>
+        <v>381181</v>
       </c>
       <c r="R43" t="n">
-        <v>6838962</v>
+        <v>6839245</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,7 +5176,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476144</v>
+        <v>129476142</v>
       </c>
       <c r="B44" t="n">
         <v>78839</v>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381292</v>
+        <v>381360</v>
       </c>
       <c r="R44" t="n">
-        <v>6838844</v>
+        <v>6838853</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476127</v>
+        <v>129476157</v>
       </c>
       <c r="B45" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381181</v>
+        <v>381464</v>
       </c>
       <c r="R45" t="n">
-        <v>6839245</v>
+        <v>6838872</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476142</v>
+        <v>129476151</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381360</v>
+        <v>381200</v>
       </c>
       <c r="R46" t="n">
-        <v>6838853</v>
+        <v>6839267</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476174</v>
+        <v>129476143</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381317</v>
+        <v>381307</v>
       </c>
       <c r="R47" t="n">
-        <v>6839120</v>
+        <v>6838866</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476149</v>
+        <v>129476174</v>
       </c>
       <c r="B48" t="n">
-        <v>78838</v>
+        <v>78484</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381441</v>
+        <v>381317</v>
       </c>
       <c r="R48" t="n">
-        <v>6838759</v>
+        <v>6839120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476143</v>
+        <v>129476149</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381307</v>
+        <v>381441</v>
       </c>
       <c r="R49" t="n">
-        <v>6838866</v>
+        <v>6838759</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476155</v>
+        <v>129476136</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381382</v>
+        <v>381421</v>
       </c>
       <c r="R57" t="n">
-        <v>6838965</v>
+        <v>6838767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,7 +6674,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476159</v>
+        <v>129476155</v>
       </c>
       <c r="B58" t="n">
         <v>78838</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381360</v>
+        <v>381382</v>
       </c>
       <c r="R58" t="n">
-        <v>6838853</v>
+        <v>6838965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476136</v>
+        <v>129476159</v>
       </c>
       <c r="B59" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381421</v>
+        <v>381360</v>
       </c>
       <c r="R59" t="n">
-        <v>6838767</v>
+        <v>6838853</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -2813,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476141</v>
+        <v>129476154</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381425</v>
+        <v>381306</v>
       </c>
       <c r="R22" t="n">
-        <v>6838921</v>
+        <v>6839044</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476154</v>
+        <v>129476141</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>381306</v>
+        <v>381425</v>
       </c>
       <c r="R23" t="n">
-        <v>6839044</v>
+        <v>6838921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476143</v>
+        <v>129476174</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>78484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>381307</v>
+        <v>381317</v>
       </c>
       <c r="R47" t="n">
-        <v>6838866</v>
+        <v>6839120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476174</v>
+        <v>129476149</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>78838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>381317</v>
+        <v>381441</v>
       </c>
       <c r="R48" t="n">
-        <v>6839120</v>
+        <v>6838759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5711,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476149</v>
+        <v>129476143</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>381441</v>
+        <v>381307</v>
       </c>
       <c r="R49" t="n">
-        <v>6838759</v>
+        <v>6838866</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476136</v>
+        <v>129476155</v>
       </c>
       <c r="B57" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381421</v>
+        <v>381382</v>
       </c>
       <c r="R57" t="n">
-        <v>6838767</v>
+        <v>6838965</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6674,7 +6674,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476155</v>
+        <v>129476159</v>
       </c>
       <c r="B58" t="n">
         <v>78838</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>381382</v>
+        <v>381360</v>
       </c>
       <c r="R58" t="n">
-        <v>6838965</v>
+        <v>6838853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129476159</v>
+        <v>129476136</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381360</v>
+        <v>381421</v>
       </c>
       <c r="R59" t="n">
-        <v>6838853</v>
+        <v>6838767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476173</v>
+        <v>129476129</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
+        <v>79671</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6899,21 +6899,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>381193</v>
+        <v>381313</v>
       </c>
       <c r="R60" t="n">
-        <v>6839219</v>
+        <v>6839168</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476129</v>
+        <v>129476126</v>
       </c>
       <c r="B61" t="n">
         <v>79671</v>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381313</v>
+        <v>381419</v>
       </c>
       <c r="R61" t="n">
-        <v>6839168</v>
+        <v>6838773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476126</v>
+        <v>129476139</v>
       </c>
       <c r="B62" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381419</v>
+        <v>381291</v>
       </c>
       <c r="R62" t="n">
-        <v>6838773</v>
+        <v>6839075</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476139</v>
+        <v>129476173</v>
       </c>
       <c r="B63" t="n">
-        <v>78839</v>
+        <v>78484</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381291</v>
+        <v>381193</v>
       </c>
       <c r="R63" t="n">
-        <v>6839075</v>
+        <v>6839219</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -2262,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476169</v>
+        <v>129476161</v>
       </c>
       <c r="B17" t="n">
-        <v>92881</v>
+        <v>79160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381326</v>
+        <v>381371</v>
       </c>
       <c r="R17" t="n">
-        <v>6838973</v>
+        <v>6838792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,8 +2351,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2369,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476161</v>
+        <v>129476148</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>81066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381371</v>
+        <v>381218</v>
       </c>
       <c r="R18" t="n">
-        <v>6838792</v>
+        <v>6838830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2455,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,7 +2465,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,24 +2474,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476148</v>
+        <v>129476162</v>
       </c>
       <c r="B19" t="n">
-        <v>81066</v>
+        <v>79160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>381218</v>
+        <v>381304</v>
       </c>
       <c r="R19" t="n">
-        <v>6838830</v>
+        <v>6838862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129476162</v>
+        <v>129476169</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>92881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>381304</v>
+        <v>381326</v>
       </c>
       <c r="R20" t="n">
-        <v>6838862</v>
+        <v>6838973</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129476131</v>
+        <v>129476150</v>
       </c>
       <c r="B24" t="n">
-        <v>90631</v>
+        <v>78838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381232</v>
+        <v>381228</v>
       </c>
       <c r="R24" t="n">
-        <v>6838826</v>
+        <v>6838960</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,7 +3134,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476150</v>
+        <v>129476156</v>
       </c>
       <c r="B25" t="n">
         <v>78838</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>381228</v>
+        <v>381423</v>
       </c>
       <c r="R25" t="n">
-        <v>6838960</v>
+        <v>6838921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476156</v>
+        <v>129476131</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>90631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381423</v>
+        <v>381232</v>
       </c>
       <c r="R26" t="n">
-        <v>6838921</v>
+        <v>6838826</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4747,32 +4747,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476146</v>
+        <v>129476157</v>
       </c>
       <c r="B40" t="n">
-        <v>91887</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>381251</v>
+        <v>381464</v>
       </c>
       <c r="R40" t="n">
-        <v>6839071</v>
+        <v>6838872</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4836,7 +4836,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4855,10 +4854,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476140</v>
+        <v>129476151</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4866,21 +4865,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4889,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381382</v>
+        <v>381200</v>
       </c>
       <c r="R41" t="n">
-        <v>6838962</v>
+        <v>6839267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4924,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4935,7 +4934,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,32 +4961,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476144</v>
+        <v>129476146</v>
       </c>
       <c r="B42" t="n">
-        <v>78839</v>
+        <v>91887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>71</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4996,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>381292</v>
+        <v>381251</v>
       </c>
       <c r="R42" t="n">
-        <v>6838844</v>
+        <v>6839071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5031,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5042,7 +5041,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5051,6 +5050,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476127</v>
+        <v>129476140</v>
       </c>
       <c r="B43" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>381181</v>
+        <v>381382</v>
       </c>
       <c r="R43" t="n">
-        <v>6839245</v>
+        <v>6838962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,7 +5176,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476142</v>
+        <v>129476144</v>
       </c>
       <c r="B44" t="n">
         <v>78839</v>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>381360</v>
+        <v>381292</v>
       </c>
       <c r="R44" t="n">
-        <v>6838853</v>
+        <v>6838844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476157</v>
+        <v>129476127</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5294,21 +5294,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>381464</v>
+        <v>381181</v>
       </c>
       <c r="R45" t="n">
-        <v>6838872</v>
+        <v>6839245</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476151</v>
+        <v>129476142</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>381200</v>
+        <v>381360</v>
       </c>
       <c r="R46" t="n">
-        <v>6839267</v>
+        <v>6838853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476164</v>
+        <v>129476138</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,21 +5829,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>381410</v>
+        <v>381200</v>
       </c>
       <c r="R50" t="n">
-        <v>6838936</v>
+        <v>6839267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476171</v>
+        <v>129476164</v>
       </c>
       <c r="B51" t="n">
-        <v>78089</v>
+        <v>79160</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>381283</v>
+        <v>381410</v>
       </c>
       <c r="R51" t="n">
-        <v>6838879</v>
+        <v>6838936</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476122</v>
+        <v>129476171</v>
       </c>
       <c r="B52" t="n">
-        <v>79700</v>
+        <v>78089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>381350</v>
+        <v>381283</v>
       </c>
       <c r="R52" t="n">
-        <v>6838974</v>
+        <v>6838879</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129476138</v>
+        <v>129476122</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381200</v>
+        <v>381350</v>
       </c>
       <c r="R53" t="n">
-        <v>6839267</v>
+        <v>6838974</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -6888,10 +6888,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476129</v>
+        <v>129476173</v>
       </c>
       <c r="B60" t="n">
-        <v>79671</v>
+        <v>78484</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6899,21 +6899,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>381313</v>
+        <v>381193</v>
       </c>
       <c r="R60" t="n">
-        <v>6839168</v>
+        <v>6839219</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476126</v>
+        <v>129476129</v>
       </c>
       <c r="B61" t="n">
         <v>79671</v>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381419</v>
+        <v>381313</v>
       </c>
       <c r="R61" t="n">
-        <v>6838773</v>
+        <v>6839168</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476139</v>
+        <v>129476126</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381291</v>
+        <v>381419</v>
       </c>
       <c r="R62" t="n">
-        <v>6839075</v>
+        <v>6838773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476173</v>
+        <v>129476139</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>78839</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381193</v>
+        <v>381291</v>
       </c>
       <c r="R63" t="n">
-        <v>6839219</v>
+        <v>6839075</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 26765-2025 artfynd.xlsx
+++ b/artfynd/A 26765-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476146</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476161</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476162</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476163</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476164</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476148</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476131</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476166</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476167</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476168</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2187,6 +2257,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476173</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476174</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783208</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476149</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476150</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476151</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2916,6 +3021,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3023,6 +3133,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476154</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476155</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3237,6 +3357,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476156</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3344,6 +3469,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476157</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3451,6 +3581,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476158</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3558,6 +3693,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476159</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476160</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3762,6 +3907,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782282</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3869,6 +4019,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782556</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3976,6 +4131,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476119</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4083,6 +4243,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476120</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4190,6 +4355,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476121</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4297,6 +4467,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476122</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4404,6 +4579,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476123</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4511,6 +4691,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476124</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4618,6 +4803,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476170</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4725,6 +4915,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476171</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4822,6 +5017,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783829</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4937,6 +5137,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476132</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5052,6 +5257,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476133</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5183,6 +5393,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783709</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5290,6 +5505,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125784308</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5397,6 +5617,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476147</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5504,6 +5729,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476135</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5611,6 +5841,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476136</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5718,6 +5953,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476137</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5825,6 +6065,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476138</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5932,6 +6177,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476139</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6039,6 +6289,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476140</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6146,6 +6401,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476141</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6253,6 +6513,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476142</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6360,6 +6625,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476143</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6467,6 +6737,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476144</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6574,6 +6849,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476145</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6671,6 +6951,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782690</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6768,6 +7053,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783196</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6875,6 +7165,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476125</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6982,6 +7277,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476126</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7089,6 +7389,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476127</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7196,6 +7501,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476128</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7303,6 +7613,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476129</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7410,6 +7725,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476130</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7517,8 +7837,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>